--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/97.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/97.xlsx
@@ -426,13 +426,13 @@
         <v>-8.368357005910219</v>
       </c>
       <c r="E2">
-        <v>-7.5671591275829</v>
+        <v>-11.5892818140856</v>
       </c>
       <c r="F2">
-        <v>-4.521200438868111</v>
+        <v>-2.636184144405612</v>
       </c>
       <c r="G2">
-        <v>-7.629938228348294</v>
+        <v>-9.071418234071071</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.436858893990856</v>
       </c>
       <c r="E3">
-        <v>-7.164233624276422</v>
+        <v>-9.939092300268495</v>
       </c>
       <c r="F3">
-        <v>-4.322237357491907</v>
+        <v>-2.724601595878223</v>
       </c>
       <c r="G3">
-        <v>-7.059606140550292</v>
+        <v>-8.969345993799864</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.465811227733951</v>
       </c>
       <c r="E4">
-        <v>-7.974386681196664</v>
+        <v>-10.75449385856363</v>
       </c>
       <c r="F4">
-        <v>-4.346050435220184</v>
+        <v>-2.97646587633201</v>
       </c>
       <c r="G4">
-        <v>-7.108269937498417</v>
+        <v>-7.917960575614792</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.449571001890366</v>
       </c>
       <c r="E5">
-        <v>-9.111830668547274</v>
+        <v>-10.76725962679125</v>
       </c>
       <c r="F5">
-        <v>-4.420725271480351</v>
+        <v>-3.586222151328309</v>
       </c>
       <c r="G5">
-        <v>-7.445011862479549</v>
+        <v>-8.695226182280734</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.383910940985865</v>
       </c>
       <c r="E6">
-        <v>-7.928214360214457</v>
+        <v>-11.10654648486794</v>
       </c>
       <c r="F6">
-        <v>-4.826980668467909</v>
+        <v>-2.500627617509293</v>
       </c>
       <c r="G6">
-        <v>-7.557026204075873</v>
+        <v>-9.439673010909111</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.266917057162651</v>
       </c>
       <c r="E7">
-        <v>-10.22021090971666</v>
+        <v>-14.53320653868003</v>
       </c>
       <c r="F7">
-        <v>-4.480972432685959</v>
+        <v>-1.611109304667725</v>
       </c>
       <c r="G7">
-        <v>-7.016782917977979</v>
+        <v>-7.166478807962966</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.099101220886782</v>
       </c>
       <c r="E8">
-        <v>-11.1671012392985</v>
+        <v>-13.98109498766486</v>
       </c>
       <c r="F8">
-        <v>-4.393572216383986</v>
+        <v>-2.746844089010793</v>
       </c>
       <c r="G8">
-        <v>-6.54523200522706</v>
+        <v>-8.238089675840456</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.883335099821155</v>
       </c>
       <c r="E9">
-        <v>-11.2906697095458</v>
+        <v>-14.3535936741138</v>
       </c>
       <c r="F9">
-        <v>-4.173842792587</v>
+        <v>-2.726802568067462</v>
       </c>
       <c r="G9">
-        <v>-6.652928259251154</v>
+        <v>-8.202373579165901</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.624621270596609</v>
       </c>
       <c r="E10">
-        <v>-10.24979995888277</v>
+        <v>-15.28952509659709</v>
       </c>
       <c r="F10">
-        <v>-4.386599847954622</v>
+        <v>-2.892876978450317</v>
       </c>
       <c r="G10">
-        <v>-5.574328389452047</v>
+        <v>-7.524414142996552</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.328621801084504</v>
       </c>
       <c r="E11">
-        <v>-13.12130985562055</v>
+        <v>-15.29429357972717</v>
       </c>
       <c r="F11">
-        <v>-3.959968269593002</v>
+        <v>-2.133708903378474</v>
       </c>
       <c r="G11">
-        <v>-4.974081404696587</v>
+        <v>-8.362644846236977</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.003609318918851</v>
       </c>
       <c r="E12">
-        <v>-13.20473793226387</v>
+        <v>-16.12284582654058</v>
       </c>
       <c r="F12">
-        <v>-4.579424726876083</v>
+        <v>-2.561125774037949</v>
       </c>
       <c r="G12">
-        <v>-4.387956797532977</v>
+        <v>-6.873386973387126</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.65688424367721</v>
       </c>
       <c r="E13">
-        <v>-15.06838612538052</v>
+        <v>-19.01112466252876</v>
       </c>
       <c r="F13">
-        <v>-4.790931775832881</v>
+        <v>-2.392655725126197</v>
       </c>
       <c r="G13">
-        <v>-3.950481370676892</v>
+        <v>-7.056167420355994</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.302060582587266</v>
       </c>
       <c r="E14">
-        <v>-17.35682329431269</v>
+        <v>-18.02149912373653</v>
       </c>
       <c r="F14">
-        <v>-4.89327076987694</v>
+        <v>-2.450387962896906</v>
       </c>
       <c r="G14">
-        <v>-3.016291342930506</v>
+        <v>-5.171046572466935</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.95091311185835</v>
       </c>
       <c r="E15">
-        <v>-16.24043671109775</v>
+        <v>-20.84404715950338</v>
       </c>
       <c r="F15">
-        <v>-4.777759905760966</v>
+        <v>-2.435647164964089</v>
       </c>
       <c r="G15">
-        <v>-2.780781665501361</v>
+        <v>-6.504180642296847</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.616789392698712</v>
       </c>
       <c r="E16">
-        <v>-18.52372953355721</v>
+        <v>-18.99637089421177</v>
       </c>
       <c r="F16">
-        <v>-4.475305571283408</v>
+        <v>-2.484129023947735</v>
       </c>
       <c r="G16">
-        <v>-1.719568988745751</v>
+        <v>-5.663374180132258</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.314318701293633</v>
       </c>
       <c r="E17">
-        <v>-18.01060361527407</v>
+        <v>-20.14353298678284</v>
       </c>
       <c r="F17">
-        <v>-4.64410116858446</v>
+        <v>-2.380729719628092</v>
       </c>
       <c r="G17">
-        <v>-2.878637536068681</v>
+        <v>-4.188238684874256</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.058234127893128</v>
       </c>
       <c r="E18">
-        <v>-19.716778653248</v>
+        <v>-22.07762159308881</v>
       </c>
       <c r="F18">
-        <v>-4.165726448774371</v>
+        <v>-1.620051530780946</v>
       </c>
       <c r="G18">
-        <v>-1.549542649978445</v>
+        <v>-3.256814726902482</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.861869159117136</v>
       </c>
       <c r="E19">
-        <v>-20.83363619775974</v>
+        <v>-21.85648715034625</v>
       </c>
       <c r="F19">
-        <v>-4.328228938916356</v>
+        <v>-2.080313168961421</v>
       </c>
       <c r="G19">
-        <v>-0.03126237243530525</v>
+        <v>-1.800447818964504</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.734461310103415</v>
       </c>
       <c r="E20">
-        <v>-20.90195275663946</v>
+        <v>-22.9159055305447</v>
       </c>
       <c r="F20">
-        <v>-3.899687973691282</v>
+        <v>-1.633675689454789</v>
       </c>
       <c r="G20">
-        <v>-0.8687679257110934</v>
+        <v>-1.366142052134842</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.680986016478454</v>
       </c>
       <c r="E21">
-        <v>-22.37653257691311</v>
+        <v>-24.21013887346288</v>
       </c>
       <c r="F21">
-        <v>-3.958266802947652</v>
+        <v>-1.35349615443851</v>
       </c>
       <c r="G21">
-        <v>-1.824509016659912</v>
+        <v>-3.169681888391428</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.701181292715046</v>
       </c>
       <c r="E22">
-        <v>-22.10814803637452</v>
+        <v>-24.83730082420717</v>
       </c>
       <c r="F22">
-        <v>-3.76267517690084</v>
+        <v>-2.514785244790539</v>
       </c>
       <c r="G22">
-        <v>-0.8253311147071642</v>
+        <v>-1.788251518428048</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.792180747964005</v>
       </c>
       <c r="E23">
-        <v>-21.5439047034928</v>
+        <v>-25.0683345111305</v>
       </c>
       <c r="F23">
-        <v>-4.004295866051609</v>
+        <v>-1.069088632198341</v>
       </c>
       <c r="G23">
-        <v>-1.340092434174411</v>
+        <v>-4.406686010194288</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.944728860652063</v>
       </c>
       <c r="E24">
-        <v>-24.68842724120501</v>
+        <v>-25.31078448102716</v>
       </c>
       <c r="F24">
-        <v>-3.536533361038784</v>
+        <v>-1.110672675818877</v>
       </c>
       <c r="G24">
-        <v>-1.221230183183526</v>
+        <v>-2.813757942173781</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.145344325943689</v>
       </c>
       <c r="E25">
-        <v>-23.85452233811454</v>
+        <v>-25.41644736504814</v>
       </c>
       <c r="F25">
-        <v>-3.472400328346643</v>
+        <v>-0.135921155801059</v>
       </c>
       <c r="G25">
-        <v>-1.655578605893461</v>
+        <v>-2.433192022044704</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.378419602254694</v>
       </c>
       <c r="E26">
-        <v>-23.88182450790678</v>
+        <v>-26.05952237345538</v>
       </c>
       <c r="F26">
-        <v>-3.687460245094048</v>
+        <v>-0.5374043281810899</v>
       </c>
       <c r="G26">
-        <v>-2.149313857607785</v>
+        <v>-2.269692032959134</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.627536656423796</v>
       </c>
       <c r="E27">
-        <v>-24.15815652032883</v>
+        <v>-27.06941736190594</v>
       </c>
       <c r="F27">
-        <v>-3.140454457594617</v>
+        <v>-0.7538857233916986</v>
       </c>
       <c r="G27">
-        <v>-1.423940769904461</v>
+        <v>-1.224088127161802</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.876875279153015</v>
       </c>
       <c r="E28">
-        <v>-23.86974706772832</v>
+        <v>-26.92664363339211</v>
       </c>
       <c r="F28">
-        <v>-3.053113055378243</v>
+        <v>-1.40476961156959</v>
       </c>
       <c r="G28">
-        <v>-1.691731105035422</v>
+        <v>-1.81548237614988</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.111692204551469</v>
       </c>
       <c r="E29">
-        <v>-23.74458457463032</v>
+        <v>-27.60288065695753</v>
       </c>
       <c r="F29">
-        <v>-3.213354102510585</v>
+        <v>-0.4539496258186508</v>
       </c>
       <c r="G29">
-        <v>-1.205719848872031</v>
+        <v>-2.411125807057439</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.319062186031345</v>
       </c>
       <c r="E30">
-        <v>-24.08412955572545</v>
+        <v>-28.18793232790449</v>
       </c>
       <c r="F30">
-        <v>-3.048962934690217</v>
+        <v>0.454198669911878</v>
       </c>
       <c r="G30">
-        <v>-0.9693242416218362</v>
+        <v>-1.317317475330305</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.49138258082924</v>
       </c>
       <c r="E31">
-        <v>-24.1205294297991</v>
+        <v>-25.04693747144426</v>
       </c>
       <c r="F31">
-        <v>-2.978248522982835</v>
+        <v>-0.6914309630576299</v>
       </c>
       <c r="G31">
-        <v>-0.7755517024288284</v>
+        <v>-2.982176482376959</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.624769522443036</v>
       </c>
       <c r="E32">
-        <v>-23.99773080013311</v>
+        <v>-26.49210485303809</v>
       </c>
       <c r="F32">
-        <v>-2.526698824777602</v>
+        <v>-0.4423036085026926</v>
       </c>
       <c r="G32">
-        <v>0.3306530843498874</v>
+        <v>-2.574990011736108</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.718563436367768</v>
       </c>
       <c r="E33">
-        <v>-22.34268223370577</v>
+        <v>-25.20175241234448</v>
       </c>
       <c r="F33">
-        <v>-2.285232211963754</v>
+        <v>-0.5435972028844189</v>
       </c>
       <c r="G33">
-        <v>-0.807540331411855</v>
+        <v>-1.386137816318098</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.774441242799586</v>
       </c>
       <c r="E34">
-        <v>-23.9361526105768</v>
+        <v>-24.1824019701659</v>
       </c>
       <c r="F34">
-        <v>-3.050430801727978</v>
+        <v>-0.7818315260925427</v>
       </c>
       <c r="G34">
-        <v>-0.2439708412478684</v>
+        <v>-2.134554923033403</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.796335456962745</v>
       </c>
       <c r="E35">
-        <v>-21.91618149471536</v>
+        <v>-22.93859771379714</v>
       </c>
       <c r="F35">
-        <v>-2.771303293313254</v>
+        <v>-0.4172115315044927</v>
       </c>
       <c r="G35">
-        <v>-1.506348649369915</v>
+        <v>-2.258827908375812</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.789681379943666</v>
       </c>
       <c r="E36">
-        <v>-20.963675857364</v>
+        <v>-23.29922274139797</v>
       </c>
       <c r="F36">
-        <v>-2.652055663843251</v>
+        <v>-1.246627647435943</v>
       </c>
       <c r="G36">
-        <v>-1.434870518918971</v>
+        <v>-2.472484650219055</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.760472160681688</v>
       </c>
       <c r="E37">
-        <v>-20.34277225769831</v>
+        <v>-27.59091642862926</v>
       </c>
       <c r="F37">
-        <v>-2.70236075948046</v>
+        <v>-0.1957557900400729</v>
       </c>
       <c r="G37">
-        <v>-1.081348426882838</v>
+        <v>-2.939244979493185</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.714483630743991</v>
       </c>
       <c r="E38">
-        <v>-19.60494798762858</v>
+        <v>-21.91405764040577</v>
       </c>
       <c r="F38">
-        <v>-2.629063498211148</v>
+        <v>-1.131241866797791</v>
       </c>
       <c r="G38">
-        <v>-0.6562038306471458</v>
+        <v>-2.099970847796856</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.655403326074286</v>
       </c>
       <c r="E39">
-        <v>-19.25251949798163</v>
+        <v>-21.91456935796863</v>
       </c>
       <c r="F39">
-        <v>-2.424629050139452</v>
+        <v>-0.3417315221288046</v>
       </c>
       <c r="G39">
-        <v>-1.018611470666255</v>
+        <v>-2.86327813794892</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.588656956182183</v>
       </c>
       <c r="E40">
-        <v>-17.99945904074119</v>
+        <v>-22.5679285308473</v>
       </c>
       <c r="F40">
-        <v>-2.346814701422675</v>
+        <v>-0.1079513304455337</v>
       </c>
       <c r="G40">
-        <v>-0.494016330185353</v>
+        <v>-2.223909148540201</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.518370159978653</v>
       </c>
       <c r="E41">
-        <v>-16.87776961446327</v>
+        <v>-20.76844881441933</v>
       </c>
       <c r="F41">
-        <v>-2.80480661291948</v>
+        <v>-1.314143732601116</v>
       </c>
       <c r="G41">
-        <v>-1.397103658769763</v>
+        <v>-3.245205765025167</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.448600989207891</v>
       </c>
       <c r="E42">
-        <v>-17.56911815579228</v>
+        <v>-19.36141118397008</v>
       </c>
       <c r="F42">
-        <v>-2.828270947971179</v>
+        <v>-0.07375135385355333</v>
       </c>
       <c r="G42">
-        <v>-1.330530954550189</v>
+        <v>-1.998403915645804</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.380944096137617</v>
       </c>
       <c r="E43">
-        <v>-17.42245899657987</v>
+        <v>-21.13986519558043</v>
       </c>
       <c r="F43">
-        <v>-2.191965497715155</v>
+        <v>-0.4636175017767238</v>
       </c>
       <c r="G43">
-        <v>-0.9516253325301913</v>
+        <v>-3.444667942402251</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.315710424784911</v>
       </c>
       <c r="E44">
-        <v>-13.62582714481511</v>
+        <v>-17.44087177189505</v>
       </c>
       <c r="F44">
-        <v>-2.05634518652882</v>
+        <v>-0.2860130455143015</v>
       </c>
       <c r="G44">
-        <v>-0.6939050663651656</v>
+        <v>-5.186858779161899</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.251900137706723</v>
       </c>
       <c r="E45">
-        <v>-14.38289742941744</v>
+        <v>-19.75130373908248</v>
       </c>
       <c r="F45">
-        <v>-2.06892974411215</v>
+        <v>-1.124582621246686</v>
       </c>
       <c r="G45">
-        <v>-0.5127586677329011</v>
+        <v>-4.15807769629984</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.187479089851673</v>
       </c>
       <c r="E46">
-        <v>-14.05063423452665</v>
+        <v>-16.86884399219415</v>
       </c>
       <c r="F46">
-        <v>-1.693888887596882</v>
+        <v>0.08107134209707706</v>
       </c>
       <c r="G46">
-        <v>-0.9308880122745008</v>
+        <v>-3.897857139306518</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.119623228016787</v>
       </c>
       <c r="E47">
-        <v>-12.73684241236934</v>
+        <v>-16.30380364788708</v>
       </c>
       <c r="F47">
-        <v>-2.2455658388807</v>
+        <v>-0.423114477616842</v>
       </c>
       <c r="G47">
-        <v>-0.3449569971828984</v>
+        <v>-2.390933169580616</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.043634302362243</v>
       </c>
       <c r="E48">
-        <v>-11.14464000822046</v>
+        <v>-13.28349262373126</v>
       </c>
       <c r="F48">
-        <v>-1.601969927112638</v>
+        <v>0.2493765458956722</v>
       </c>
       <c r="G48">
-        <v>-1.420262520536324</v>
+        <v>-3.851483635006886</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.957588414568074</v>
       </c>
       <c r="E49">
-        <v>-10.26448127161564</v>
+        <v>-14.97263154248833</v>
       </c>
       <c r="F49">
-        <v>-2.127805128898722</v>
+        <v>-0.250280589227142</v>
       </c>
       <c r="G49">
-        <v>-2.085372693078886</v>
+        <v>-4.205435567067306</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.859841021932441</v>
       </c>
       <c r="E50">
-        <v>-9.787302380005393</v>
+        <v>-13.97355054996808</v>
       </c>
       <c r="F50">
-        <v>-2.213013485052888</v>
+        <v>0.1213233709339106</v>
       </c>
       <c r="G50">
-        <v>-0.5777826353764171</v>
+        <v>-5.156215451018245</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.752534797228344</v>
       </c>
       <c r="E51">
-        <v>-9.308180773045853</v>
+        <v>-15.4903810327333</v>
       </c>
       <c r="F51">
-        <v>-1.625541121559298</v>
+        <v>0.3911599105588356</v>
       </c>
       <c r="G51">
-        <v>-2.166641988663213</v>
+        <v>-5.027729377193508</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.637655675049912</v>
       </c>
       <c r="E52">
-        <v>-8.954810360805311</v>
+        <v>-12.39248366340406</v>
       </c>
       <c r="F52">
-        <v>-1.507959338936325</v>
+        <v>-0.1133498008095781</v>
       </c>
       <c r="G52">
-        <v>-2.99889430622233</v>
+        <v>-3.404420478754103</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.518550005752034</v>
       </c>
       <c r="E53">
-        <v>-7.452543450448763</v>
+        <v>-11.63731080941095</v>
       </c>
       <c r="F53">
-        <v>-1.793503381253134</v>
+        <v>0.3369358087389828</v>
       </c>
       <c r="G53">
-        <v>-2.611805317633078</v>
+        <v>-5.342775865223593</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.399729027430598</v>
       </c>
       <c r="E54">
-        <v>-7.066658594833148</v>
+        <v>-10.43173593061494</v>
       </c>
       <c r="F54">
-        <v>-1.537631459304603</v>
+        <v>-0.4121791995324858</v>
       </c>
       <c r="G54">
-        <v>-2.455474797654893</v>
+        <v>-3.961030497990507</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.28650382823307</v>
       </c>
       <c r="E55">
-        <v>-6.638228725915472</v>
+        <v>-8.602540367748635</v>
       </c>
       <c r="F55">
-        <v>-1.49140524475878</v>
+        <v>-0.1853349281128552</v>
       </c>
       <c r="G55">
-        <v>-2.462024115887545</v>
+        <v>-3.843310112102309</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.184522885699609</v>
       </c>
       <c r="E56">
-        <v>-4.727565915651179</v>
+        <v>-10.34629721151222</v>
       </c>
       <c r="F56">
-        <v>-1.41549862617065</v>
+        <v>0.2169782684047807</v>
       </c>
       <c r="G56">
-        <v>-2.335634742639294</v>
+        <v>-4.708545268776964</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.0978455668378</v>
       </c>
       <c r="E57">
-        <v>-4.486148437828264</v>
+        <v>-8.254409399934968</v>
       </c>
       <c r="F57">
-        <v>-1.696970414335297</v>
+        <v>-0.09057632417181409</v>
       </c>
       <c r="G57">
-        <v>-3.221128161221961</v>
+        <v>-3.696334354790102</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.031699068221092</v>
       </c>
       <c r="E58">
-        <v>-3.714197587636729</v>
+        <v>-5.11936495832081</v>
       </c>
       <c r="F58">
-        <v>-1.982889707085574</v>
+        <v>0.3328618978520148</v>
       </c>
       <c r="G58">
-        <v>-3.591414014205297</v>
+        <v>-5.948912642678255</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.989497940467692</v>
       </c>
       <c r="E59">
-        <v>-4.705249595741379</v>
+        <v>-7.786079146535708</v>
       </c>
       <c r="F59">
-        <v>-1.480493989329104</v>
+        <v>-0.06903960006642974</v>
       </c>
       <c r="G59">
-        <v>-2.98536254851118</v>
+        <v>-5.797641766344736</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.97623533495784</v>
       </c>
       <c r="E60">
-        <v>-3.062980382963694</v>
+        <v>-4.884740191509402</v>
       </c>
       <c r="F60">
-        <v>-1.341750733034215</v>
+        <v>-0.1598775410900207</v>
       </c>
       <c r="G60">
-        <v>-4.38788461065867</v>
+        <v>-7.11782157345796</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.993186835033329</v>
       </c>
       <c r="E61">
-        <v>-2.104057897943465</v>
+        <v>-7.579028257957003</v>
       </c>
       <c r="F61">
-        <v>-1.267436236594266</v>
+        <v>-0.3671193262898039</v>
       </c>
       <c r="G61">
-        <v>-3.768678727732738</v>
+        <v>-5.722649447603627</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.039692051869882</v>
       </c>
       <c r="E62">
-        <v>-1.823197411513741</v>
+        <v>-5.47892126605583</v>
       </c>
       <c r="F62">
-        <v>-1.680198459530815</v>
+        <v>0.2120594227669573</v>
       </c>
       <c r="G62">
-        <v>-4.59039176164292</v>
+        <v>-6.263470228695983</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.113350829330115</v>
       </c>
       <c r="E63">
-        <v>-0.7632356144343717</v>
+        <v>-5.96917839060023</v>
       </c>
       <c r="F63">
-        <v>-1.108721042217881</v>
+        <v>0.5691429307243374</v>
       </c>
       <c r="G63">
-        <v>-4.606870056314451</v>
+        <v>-6.88606561349282</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.210217520532967</v>
       </c>
       <c r="E64">
-        <v>-0.5067202042698843</v>
+        <v>-5.107812821127244</v>
       </c>
       <c r="F64">
-        <v>-1.909919650940368</v>
+        <v>0.5839417143753506</v>
       </c>
       <c r="G64">
-        <v>-4.402436828274808</v>
+        <v>-5.419412075965983</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.325301700218565</v>
       </c>
       <c r="E65">
-        <v>-0.4427962651776095</v>
+        <v>-6.989176404561909</v>
       </c>
       <c r="F65">
-        <v>-1.442175370010405</v>
+        <v>-0.1134707424503868</v>
       </c>
       <c r="G65">
-        <v>-3.32111682580292</v>
+        <v>-7.506200082120074</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.451766346720738</v>
       </c>
       <c r="E66">
-        <v>0.8225635274676648</v>
+        <v>-2.62886727916639</v>
       </c>
       <c r="F66">
-        <v>-1.466554222674795</v>
+        <v>0.6086154658351366</v>
       </c>
       <c r="G66">
-        <v>-4.439603224878637</v>
+        <v>-6.556079723702585</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.583743669046248</v>
       </c>
       <c r="E67">
-        <v>0.5957639637415103</v>
+        <v>-2.515492403910355</v>
       </c>
       <c r="F67">
-        <v>-1.362990901609398</v>
+        <v>0.4827516659189741</v>
       </c>
       <c r="G67">
-        <v>-4.366340109899356</v>
+        <v>-7.754237463463179</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.715608488245925</v>
       </c>
       <c r="E68">
-        <v>0.900507622087687</v>
+        <v>-5.752907528941909</v>
       </c>
       <c r="F68">
-        <v>-1.453659855682817</v>
+        <v>0.2349770353328084</v>
       </c>
       <c r="G68">
-        <v>-5.207875003250142</v>
+        <v>-7.452568515730951</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.844613494470096</v>
       </c>
       <c r="E69">
-        <v>0.5757118808355459</v>
+        <v>-2.36252055193125</v>
       </c>
       <c r="F69">
-        <v>-1.485428573947581</v>
+        <v>0.139492781546915</v>
       </c>
       <c r="G69">
-        <v>-4.378021258650979</v>
+        <v>-7.886214757027164</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.967499938596014</v>
       </c>
       <c r="E70">
-        <v>-0.4835389458246197</v>
+        <v>-4.999659276402053</v>
       </c>
       <c r="F70">
-        <v>-1.350113930332879</v>
+        <v>-0.3831349816555295</v>
       </c>
       <c r="G70">
-        <v>-4.479059914130961</v>
+        <v>-5.244844526560406</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.082268632314332</v>
       </c>
       <c r="E71">
-        <v>0.5862858676434562</v>
+        <v>-1.974557126746115</v>
       </c>
       <c r="F71">
-        <v>-1.872580161891778</v>
+        <v>0.2845200329594412</v>
       </c>
       <c r="G71">
-        <v>-3.695057959603478</v>
+        <v>-8.720081435593528</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.188240754006674</v>
       </c>
       <c r="E72">
-        <v>0.3836547696962384</v>
+        <v>-2.605604508188987</v>
       </c>
       <c r="F72">
-        <v>-1.612087606570431</v>
+        <v>-0.6569112366481689</v>
       </c>
       <c r="G72">
-        <v>-4.423918985824492</v>
+        <v>-6.772620659296579</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.286095458308613</v>
       </c>
       <c r="E73">
-        <v>-0.9568776914763638</v>
+        <v>-5.393387448998952</v>
       </c>
       <c r="F73">
-        <v>-2.153392569603796</v>
+        <v>-0.5012966214604622</v>
       </c>
       <c r="G73">
-        <v>-3.906785343169767</v>
+        <v>-6.148204196534249</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.377718404839913</v>
       </c>
       <c r="E74">
-        <v>0.4819317126107005</v>
+        <v>-5.21385609696486</v>
       </c>
       <c r="F74">
-        <v>-1.888720900735326</v>
+        <v>-0.8566355876675465</v>
       </c>
       <c r="G74">
-        <v>-3.21162246236425</v>
+        <v>-7.62381546891837</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.465136545054843</v>
       </c>
       <c r="E75">
-        <v>1.036805632770549</v>
+        <v>-3.905792794427255</v>
       </c>
       <c r="F75">
-        <v>-2.288112445423288</v>
+        <v>-0.6267048193050849</v>
       </c>
       <c r="G75">
-        <v>-3.461999354679238</v>
+        <v>-7.090813838802171</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.550787949503097</v>
       </c>
       <c r="E76">
-        <v>-1.570141755491114</v>
+        <v>-2.100983064092257</v>
       </c>
       <c r="F76">
-        <v>-2.218249595405983</v>
+        <v>-1.281651021226306</v>
       </c>
       <c r="G76">
-        <v>-3.88070947543686</v>
+        <v>-5.342493680169481</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.63909286086633</v>
       </c>
       <c r="E77">
-        <v>-1.413868645960418</v>
+        <v>-3.071009367379293</v>
       </c>
       <c r="F77">
-        <v>-2.365523379214902</v>
+        <v>-0.7834244766081262</v>
       </c>
       <c r="G77">
-        <v>-4.672202458784555</v>
+        <v>-6.353205075903677</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.73539622595302</v>
       </c>
       <c r="E78">
-        <v>-1.511344048975522</v>
+        <v>-4.179380551600659</v>
       </c>
       <c r="F78">
-        <v>-2.478398378255168</v>
+        <v>-0.8636062993621043</v>
       </c>
       <c r="G78">
-        <v>-2.986822692105133</v>
+        <v>-3.458130794460653</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.844202961128516</v>
       </c>
       <c r="E79">
-        <v>-2.458089467389126</v>
+        <v>-6.769395975547644</v>
       </c>
       <c r="F79">
-        <v>-2.888475034071841</v>
+        <v>-1.053990807914918</v>
       </c>
       <c r="G79">
-        <v>-2.231108148641623</v>
+        <v>-3.409729495237284</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.96903143153239</v>
       </c>
       <c r="E80">
-        <v>-2.867386533624396</v>
+        <v>-9.435987894964333</v>
       </c>
       <c r="F80">
-        <v>-2.711909350532529</v>
+        <v>-1.172757155923894</v>
       </c>
       <c r="G80">
-        <v>-2.272602476482361</v>
+        <v>-5.183265841554307</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.112649318214482</v>
       </c>
       <c r="E81">
-        <v>-2.95397548512506</v>
+        <v>-5.833958156731193</v>
       </c>
       <c r="F81">
-        <v>-2.818366158935905</v>
+        <v>-1.147767796483641</v>
       </c>
       <c r="G81">
-        <v>-1.970631656366664</v>
+        <v>-4.655297605310295</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.276968355582857</v>
       </c>
       <c r="E82">
-        <v>-4.638916508477024</v>
+        <v>-7.338724784739976</v>
       </c>
       <c r="F82">
-        <v>-3.528910724198223</v>
+        <v>-2.258912494474606</v>
       </c>
       <c r="G82">
-        <v>-2.402437132368029</v>
+        <v>-3.087064010746169</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.463064539940325</v>
       </c>
       <c r="E83">
-        <v>-5.366619639139612</v>
+        <v>-7.139068894215797</v>
       </c>
       <c r="F83">
-        <v>-3.167870105157669</v>
+        <v>-1.65176723353193</v>
       </c>
       <c r="G83">
-        <v>-2.246211611479747</v>
+        <v>-2.733961915069645</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.670653768959419</v>
       </c>
       <c r="E84">
-        <v>-6.272780873496473</v>
+        <v>-12.87916782195641</v>
       </c>
       <c r="F84">
-        <v>-3.88588985786285</v>
+        <v>-2.005499166977584</v>
       </c>
       <c r="G84">
-        <v>-1.664286967912227</v>
+        <v>-1.83852967638342</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.896591225754308</v>
       </c>
       <c r="E85">
-        <v>-7.146595218016546</v>
+        <v>-9.268869090185266</v>
       </c>
       <c r="F85">
-        <v>-3.806655687417674</v>
+        <v>-2.737218459790263</v>
       </c>
       <c r="G85">
-        <v>-0.8287567100152246</v>
+        <v>-2.352031006771839</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.142083584832418</v>
       </c>
       <c r="E86">
-        <v>-8.061822457336763</v>
+        <v>-13.52484217444406</v>
       </c>
       <c r="F86">
-        <v>-4.526420810240554</v>
+        <v>-2.968948442151605</v>
       </c>
       <c r="G86">
-        <v>-0.8241465937242047</v>
+        <v>-2.199756076641129</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.407310303115402</v>
       </c>
       <c r="E87">
-        <v>-9.726466860186349</v>
+        <v>-14.25856364706284</v>
       </c>
       <c r="F87">
-        <v>-4.248860572951926</v>
+        <v>-2.702333423356167</v>
       </c>
       <c r="G87">
-        <v>-0.4997158120341084</v>
+        <v>-3.082286552155618</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.692883841442267</v>
       </c>
       <c r="E88">
-        <v>-9.923872099128715</v>
+        <v>-11.5036800699186</v>
       </c>
       <c r="F88">
-        <v>-4.333348249465656</v>
+        <v>-3.017319299903276</v>
       </c>
       <c r="G88">
-        <v>-0.9614329037713716</v>
+        <v>-1.304379618721415</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.998566139346229</v>
       </c>
       <c r="E89">
-        <v>-11.09903827496322</v>
+        <v>-15.08441692336768</v>
       </c>
       <c r="F89">
-        <v>-5.098026624500922</v>
+        <v>-3.074683742547142</v>
       </c>
       <c r="G89">
-        <v>-0.07549652027817946</v>
+        <v>-0.5632074492093637</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.324143195884757</v>
       </c>
       <c r="E90">
-        <v>-13.43216695387709</v>
+        <v>-16.76828016990581</v>
       </c>
       <c r="F90">
-        <v>-5.275545758920856</v>
+        <v>-3.191226752447004</v>
       </c>
       <c r="G90">
-        <v>-0.3293679135539765</v>
+        <v>-2.723452162414743</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.669818006447302</v>
       </c>
       <c r="E91">
-        <v>-16.63303276519273</v>
+        <v>-18.90493194704889</v>
       </c>
       <c r="F91">
-        <v>-5.665760649520605</v>
+        <v>-3.579364925967935</v>
       </c>
       <c r="G91">
-        <v>0.2664231723237571</v>
+        <v>0.07716559399654538</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.03576689993631</v>
       </c>
       <c r="E92">
-        <v>-19.07005822326458</v>
+        <v>-17.36057739926505</v>
       </c>
       <c r="F92">
-        <v>-6.259116078308877</v>
+        <v>-4.134455579318689</v>
       </c>
       <c r="G92">
-        <v>0.38192873365933</v>
+        <v>-0.7286958585599579</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.42181535871795</v>
       </c>
       <c r="E93">
-        <v>-19.21251948707188</v>
+        <v>-22.68930069120088</v>
       </c>
       <c r="F93">
-        <v>-6.39934294062218</v>
+        <v>-4.14567912925922</v>
       </c>
       <c r="G93">
-        <v>-0.3754329830270209</v>
+        <v>-2.687854189716328</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.82164302236143</v>
       </c>
       <c r="E94">
-        <v>-20.22694747800413</v>
+        <v>-25.58685837043078</v>
       </c>
       <c r="F94">
-        <v>-6.873078802976592</v>
+        <v>-4.355755587711383</v>
       </c>
       <c r="G94">
-        <v>-1.006628449531163</v>
+        <v>-0.9531707878846898</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.2359357323622</v>
       </c>
       <c r="E95">
-        <v>-22.99085177537165</v>
+        <v>-25.3086787406136</v>
       </c>
       <c r="F95">
-        <v>-7.392255173395273</v>
+        <v>-5.580100833131914</v>
       </c>
       <c r="G95">
-        <v>-0.7746067106197084</v>
+        <v>-1.377544297053913</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.66204167679992</v>
       </c>
       <c r="E96">
-        <v>-26.65872099720231</v>
+        <v>-28.59195825039484</v>
       </c>
       <c r="F96">
-        <v>-7.354769063316387</v>
+        <v>-5.249699867586108</v>
       </c>
       <c r="G96">
-        <v>-0.7158761259272074</v>
+        <v>-1.170787964150182</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.09542496656322</v>
       </c>
       <c r="E97">
-        <v>-27.66463998547414</v>
+        <v>-29.72853277073597</v>
       </c>
       <c r="F97">
-        <v>-7.595794156304541</v>
+        <v>-5.442245586692826</v>
       </c>
       <c r="G97">
-        <v>-1.080829993876446</v>
+        <v>-2.752359724353451</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.53273887486899</v>
       </c>
       <c r="E98">
-        <v>-29.15086251242151</v>
+        <v>-31.33053932111146</v>
       </c>
       <c r="F98">
-        <v>-7.937936401417627</v>
+        <v>-6.05033435810729</v>
       </c>
       <c r="G98">
-        <v>-2.109588108187588</v>
+        <v>-4.489271075623952</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.96174244211023</v>
       </c>
       <c r="E99">
-        <v>-33.50390796550872</v>
+        <v>-34.17827020083497</v>
       </c>
       <c r="F99">
-        <v>-7.513238232574141</v>
+        <v>-6.529939617694238</v>
       </c>
       <c r="G99">
-        <v>-1.536329170758561</v>
+        <v>-2.928354605137387</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.38046946086995</v>
       </c>
       <c r="E100">
-        <v>-34.88522839206841</v>
+        <v>-39.32221590359881</v>
       </c>
       <c r="F100">
-        <v>-8.77966247113838</v>
+        <v>-6.009352537588589</v>
       </c>
       <c r="G100">
-        <v>-2.434048420871719</v>
+        <v>-2.873233364160276</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.76812715732687</v>
       </c>
       <c r="E101">
-        <v>-38.12406545793838</v>
+        <v>-40.00726533758316</v>
       </c>
       <c r="F101">
-        <v>-8.420798801632383</v>
+        <v>-6.664640441063465</v>
       </c>
       <c r="G101">
-        <v>-2.960848542240568</v>
+        <v>-3.168494086186909</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.13200556023539</v>
       </c>
       <c r="E102">
-        <v>-38.5196933253815</v>
+        <v>-41.94844779842214</v>
       </c>
       <c r="F102">
-        <v>-8.187739289589548</v>
+        <v>-5.934196419867396</v>
       </c>
       <c r="G102">
-        <v>-3.704327410508909</v>
+        <v>-2.915380655091343</v>
       </c>
     </row>
   </sheetData>
